--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -416,11 +416,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,7 +531,24 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>draws</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$H$2:$H$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1013,9 +1030,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1078,9 +1092,6 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1143,9 +1154,6 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1208,9 +1216,6 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1263,12 +1268,6 @@
           <t>0.12</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1326,12 +1325,6 @@
           <t>0.65</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v/>
-      </c>
-      <c r="I7" t="n">
-        <v/>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1399,9 +1392,6 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1464,9 +1454,6 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1529,9 +1516,6 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1594,9 +1578,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1659,9 +1640,6 @@
           <t>0.96</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1724,9 +1702,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1789,9 +1764,6 @@
           <t>0.2</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1854,9 +1826,6 @@
           <t>0.2</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1919,9 +1888,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1984,9 +1950,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v/>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2049,9 +2012,6 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v/>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2114,9 +2074,6 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v/>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2179,9 +2136,6 @@
           <t>0.98</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v/>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2234,12 +2188,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v/>
-      </c>
-      <c r="I21" t="n">
-        <v/>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>1</t>
@@ -2297,12 +2245,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v/>
-      </c>
-      <c r="I22" t="n">
-        <v/>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>1</t>
@@ -2360,12 +2302,6 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v/>
-      </c>
-      <c r="I23" t="n">
-        <v/>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>1</t>
@@ -2423,12 +2359,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v/>
-      </c>
-      <c r="I24" t="n">
-        <v/>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>1</t>
@@ -2486,12 +2416,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v/>
-      </c>
-      <c r="I25" t="n">
-        <v/>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>1</t>
@@ -2549,12 +2473,6 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v/>
-      </c>
-      <c r="I26" t="n">
-        <v/>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>1</t>
@@ -2612,12 +2530,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v/>
-      </c>
-      <c r="I27" t="n">
-        <v/>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>1</t>
@@ -2675,12 +2587,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v/>
-      </c>
-      <c r="I28" t="n">
-        <v/>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>1</t>
@@ -2738,12 +2644,6 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v/>
-      </c>
-      <c r="I29" t="n">
-        <v/>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>1</t>
@@ -2811,9 +2711,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v/>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2866,12 +2763,6 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v/>
-      </c>
-      <c r="I31" t="n">
-        <v/>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>1</t>
@@ -2939,9 +2830,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v/>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3004,9 +2892,6 @@
           <t>0.35</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v/>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3069,9 +2954,6 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v/>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3134,9 +3016,6 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v/>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3199,9 +3078,6 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v/>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3264,9 +3140,6 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v/>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3329,9 +3202,6 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v/>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3394,9 +3264,6 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v/>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3459,9 +3326,6 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v/>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3524,9 +3388,6 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v/>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3589,9 +3450,6 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v/>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3644,12 +3502,6 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v/>
-      </c>
-      <c r="I43" t="n">
-        <v/>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>1</t>
@@ -3707,12 +3559,6 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v/>
-      </c>
-      <c r="I44" t="n">
-        <v/>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>1</t>
@@ -3770,12 +3616,6 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v/>
-      </c>
-      <c r="I45" t="n">
-        <v/>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>1</t>
@@ -3833,12 +3673,6 @@
           <t>0.99</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v/>
-      </c>
-      <c r="I46" t="n">
-        <v/>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>1</t>
@@ -3896,12 +3730,6 @@
           <t>0.98</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v/>
-      </c>
-      <c r="I47" t="n">
-        <v/>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>1</t>
@@ -3959,12 +3787,6 @@
           <t>0.98</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v/>
-      </c>
-      <c r="I48" t="n">
-        <v/>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>1</t>
@@ -4022,12 +3844,6 @@
           <t>0.99</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v/>
-      </c>
-      <c r="I49" t="n">
-        <v/>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>1</t>
@@ -4085,12 +3901,6 @@
           <t>0.99</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v/>
-      </c>
-      <c r="I50" t="n">
-        <v/>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>1</t>
@@ -4148,12 +3958,6 @@
           <t>0.99</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v/>
-      </c>
-      <c r="I51" t="n">
-        <v/>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>1</t>
@@ -4221,9 +4025,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v/>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -4275,12 +4076,6 @@
         <is>
           <t>0.45</t>
         </is>
-      </c>
-      <c r="H53" t="n">
-        <v/>
-      </c>
-      <c r="I53" t="n">
-        <v/>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4337,7 +4132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4376,6 +4171,11 @@
           <t>is_residual</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>child_layer</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4408,7 +4208,11 @@
           <t>component</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4444,6 +4248,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>material</t>
         </is>
       </c>
     </row>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,12 +434,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -572,37 +582,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>keyed_at</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>is_loss</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -918,67 +928,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Input_layer</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Input_layer_key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>TC_target_layer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>TC_target_key</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>value_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>value_max</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_residual</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -569,16 +569,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,11 +608,6 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_loss</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>role</t>
         </is>
       </c>
@@ -644,10 +638,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>intermediate</t>
         </is>
@@ -679,10 +670,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>handoff</t>
         </is>
@@ -714,10 +702,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>intermediate</t>
         </is>
@@ -749,10 +734,7 @@
           <t>component</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
@@ -784,10 +766,7 @@
           <t>element</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>recovered</t>
         </is>
@@ -819,10 +798,7 @@
           <t>element</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
@@ -854,10 +830,7 @@
           <t>element</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>recovered</t>
         </is>
@@ -889,10 +862,7 @@
           <t>element</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>loss</t>
         </is>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -869,6 +869,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="E2:E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$I$2:$I$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$J$2:$J$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4112,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4156,6 +4164,16 @@
           <t>child_layer</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>keyed_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4193,6 +4211,16 @@
           <t>element</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4235,6 +4263,16 @@
           <t>material</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4272,6 +4310,16 @@
           <t>FALSE</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>handoff</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4287,6 +4335,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>Dy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>intermediate</t>
         </is>
       </c>
     </row>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -2176,11 +2176,13 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2193,7 +2195,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: a stand-in range so conditioning can be tried. NOT a refining measurement.</t>
         </is>
       </c>
     </row>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -2176,13 +2176,11 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2195,7 +2193,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: a stand-in range so conditioning can be tried. NOT a refining measurement.</t>
+          <t>derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -572,12 +572,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,7 +684,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -711,32 +711,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>recovered</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -768,29 +768,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>loss</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>recovered</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -832,39 +832,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>loss</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -890,19 +890,19 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,7 @@
           <t>0.95</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1080,6 +1081,7 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1142,6 +1144,7 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1204,6 +1207,7 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1238,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1253,14 +1257,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.1125</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.3625</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1273,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>derived: stays in the hulk</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: whatever is not pulled out is left in the car</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1305,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1310,14 +1320,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.775</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1330,131 +1346,133 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>derived: what is neither removed nor lost stays in the hulk</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: whatever is not pulled out is left in the car</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: losses during dismantling</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium oxidises to slag in a pyro route</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: losses during dismantling</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: reports to the copper matte</t>
         </is>
       </c>
     </row>
@@ -1486,24 +1504,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.3</t>
-        </is>
-      </c>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1516,7 +1535,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium oxidises to slag in a pyro route</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: winding copper, bound up with steel and magnets</t>
         </is>
       </c>
     </row>
@@ -1548,24 +1567,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1578,7 +1598,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: reports to the copper matte</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -1610,24 +1630,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.96</t>
-        </is>
-      </c>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1640,7 +1661,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: winding copper, bound up with steel and magnets</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1693,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1687,9 +1708,10 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1702,7 +1724,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1756,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1749,9 +1771,10 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1764,7 +1787,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: copper smelter sends rare earths to slag; dedicated magnet recovery does not. The range spans both</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1819,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1811,9 +1834,10 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1826,7 +1850,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1882,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1876,6 +1900,7 @@
           <t>0.6</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1888,7 +1913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: copper smelter sends rare earths to slag; dedicated magnet recovery does not. The range spans both</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1945,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1935,9 +1960,10 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1950,7 +1976,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1993,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1982,24 +2008,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2012,7 +2039,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: clean harness copper into a copper smelter</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2061,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2044,24 +2071,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2074,7 +2102,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2119,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2106,24 +2134,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.1125</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.98</t>
-        </is>
-      </c>
+          <t>0.3625</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2136,7 +2165,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: clean harness copper into a copper smelter</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2168,19 +2197,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.325</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2193,7 +2228,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2225,19 +2260,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2250,7 +2291,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2282,19 +2323,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.9625</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2307,7 +2354,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2339,19 +2386,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.9625</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2364,7 +2417,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2396,19 +2449,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2421,7 +2480,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2453,19 +2512,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2478,7 +2543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2575,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2518,11 +2583,17 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2535,7 +2606,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2567,19 +2638,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2592,7 +2669,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2686,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2624,19 +2701,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.0375</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.2875</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2649,14 +2732,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2671,7 +2754,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2681,44 +2764,45 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium separates reasonably well</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2728,12 +2812,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2743,32 +2827,38 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: largely follows the ferrous fraction</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2890,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2818,6 +2908,7 @@
           <t>0.7</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -2830,7 +2921,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium separates reasonably well</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: more of it trapped with the ferrous fraction</t>
         </is>
       </c>
     </row>
@@ -2862,24 +2953,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -2892,7 +2984,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: largely follows the ferrous fraction</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -2924,24 +3016,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -2954,7 +3047,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: more of it trapped with the ferrous fraction</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
         </is>
       </c>
     </row>
@@ -2986,12 +3079,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,9 +3094,10 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3016,7 +3110,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3142,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3063,9 +3157,10 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3078,7 +3173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: a shredded magnet disperses and is lost</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3205,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3125,9 +3220,10 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3140,7 +3236,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3190,6 +3286,7 @@
           <t>0.05</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3202,7 +3299,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: a shredded magnet disperses and is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3331,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3249,9 +3346,10 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3264,7 +3362,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3379,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3296,24 +3394,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3326,7 +3425,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: harness copper partly recovered from the non-ferrous fraction, partly lost to shredder residue</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3447,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3358,24 +3457,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3388,7 +3488,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3505,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3420,24 +3520,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.6375</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.75</t>
-        </is>
-      </c>
+          <t>0.8875</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3450,7 +3551,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: harness copper partly recovered from the non-ferrous fraction, partly lost to shredder residue</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3583,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3490,11 +3591,17 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3507,7 +3614,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3539,19 +3646,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3564,7 +3677,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3596,19 +3709,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3621,7 +3740,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3653,19 +3772,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3678,7 +3803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3710,19 +3835,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3735,7 +3866,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3767,19 +3898,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3792,7 +3929,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3961,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3832,11 +3969,17 @@
           <t>0.99</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3849,7 +3992,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -3881,19 +4024,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3906,7 +4055,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -3923,7 +4072,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3938,19 +4087,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.3375</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.5875</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3963,39 +4118,39 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Motors_mixed</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4003,113 +4158,81 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Wiring_mixed</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>derived: what is not recovered is lost</t>
+          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation sqref="A2:A53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$A$2:$A$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="B2:B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$B$2:$B$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$C$2:$C$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$D$2:$D$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$E$2:$E$13</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$F$2:$F$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$G$2:$G$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -887,22 +887,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium oxidises to slag in a pyro route</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: winding copper, bound up with steel and magnets</t>
         </is>
       </c>
     </row>
@@ -1441,22 +1441,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: reports to the copper matte</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: winding copper, bound up with steel and magnets</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: clean harness copper into a copper smelter</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>bulk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1567,24 +1567,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dy</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -1596,11 +1584,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1615,7 +1599,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>cfsteel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1630,24 +1614,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ga</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -1659,11 +1631,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1678,7 +1646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>esteel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1693,24 +1661,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nb</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -1722,11 +1678,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1741,7 +1693,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1756,24 +1708,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nd</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -1785,11 +1725,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: copper smelter sends rare earths to slag; dedicated magnet recovery does not. The range spans both</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1809,7 +1745,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1819,7 +1755,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1829,12 +1765,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1850,7 +1786,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1808,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1882,22 +1818,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1913,7 +1849,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1866,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1945,22 +1881,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0375</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2875</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1976,7 +1912,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1929,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>bulk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2008,24 +1944,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -2037,11 +1961,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: clean harness copper into a copper smelter</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2056,7 +1976,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>cfsteel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2071,24 +1991,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.925</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
@@ -2100,11 +2008,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2119,7 +2023,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>esteel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2134,24 +2038,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.1125</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.3625</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2163,11 +2055,7 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2182,7 +2070,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2197,24 +2085,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -2226,16 +2102,12 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2250,7 +2122,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2260,45 +2132,45 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: more of it trapped with the ferrous fraction</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2313,7 +2185,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2323,45 +2195,45 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.7125</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.9625</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,12 +2243,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2386,45 +2258,45 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.7125</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.9625</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: harness copper partly recovered from the non-ferrous fraction, partly lost to shredder residue</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2434,12 +2306,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>bulk</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2449,45 +2321,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nd</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.925</t>
-        </is>
-      </c>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>pyro</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
-        </is>
-      </c>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2497,12 +2353,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>cfsteel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2512,45 +2368,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pr</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0.925</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>pyro</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
-        </is>
-      </c>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2560,12 +2400,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>esteel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2575,45 +2415,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tb</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.925</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>pyro</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
-        </is>
-      </c>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2623,12 +2447,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2638,45 +2462,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>pyro</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>decision: unspecified material is not recovered</t>
-        </is>
-      </c>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2686,12 +2494,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2706,28 +2514,28 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.0375</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.2875</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2754,7 +2562,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2764,22 +2572,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -2795,7 +2603,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium separates reasonably well</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -2812,12 +2620,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2827,22 +2635,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5875</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2858,7 +2666,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: largely follows the ferrous fraction</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
@@ -2875,12 +2683,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>bulk</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2890,24 +2698,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -2919,11 +2715,7 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: more of it trapped with the ferrous fraction</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2938,12 +2730,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>cfsteel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2953,24 +2745,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dy</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -2982,11 +2762,7 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3001,12 +2777,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>esteel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3016,24 +2792,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ga</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -3045,11 +2809,7 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3064,12 +2824,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3079,24 +2839,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nb</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
@@ -3108,142 +2856,122 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Motors_mixed</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>F_recovered_shredder</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: a shredded magnet disperses and is lost</t>
+          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Motors_mixed</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>F_recovered_shredder</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3258,7 +2986,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3268,45 +2996,45 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium oxidises to slag in a pyro route</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3321,7 +3049,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3331,45 +3059,45 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: reports to the copper matte</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3379,12 +3107,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3394,45 +3122,45 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: harness copper partly recovered from the non-ferrous fraction, partly lost to shredder residue</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3447,7 +3175,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3457,45 +3185,45 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3510,7 +3238,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3520,45 +3248,45 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.6375</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.8875</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3573,7 +3301,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3583,45 +3311,45 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: copper smelter sends rare earths to slag; dedicated magnet recovery does not. The range spans both</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3636,7 +3364,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3646,45 +3374,45 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.7425</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.9925</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3699,7 +3427,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3709,45 +3437,45 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3762,7 +3490,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3772,33 +3500,33 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3810,7 +3538,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3825,7 +3553,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3835,33 +3563,33 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.7425</t>
+          <t>0.1125</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.9925</t>
+          <t>0.3625</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3873,7 +3601,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3888,7 +3616,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3898,33 +3626,33 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.7425</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.9925</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3936,7 +3664,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3951,7 +3679,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3961,33 +3689,33 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.7425</t>
+          <t>0.7125</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.9925</t>
+          <t>0.9625</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3999,7 +3727,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4014,7 +3742,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4024,45 +3752,45 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7125</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9625</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4072,12 +3800,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4087,33 +3815,33 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.5875</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4125,114 +3853,1161 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>hulk_transfer</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>definitional</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>hulk_transfer</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>definitional</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium separates reasonably well</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: largely follows the ferrous fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nb</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: a shredded magnet disperses and is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pr</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>F_recovered_shredder</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tb</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.6375</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.8875</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nb</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Pr</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Motors_mixed</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tb</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>shredding</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hammer_mill</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER: measured in its own right, not derived. Was: derived: what is not recovered is lost</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="A2:A69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$A$2:$A$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$B$2:$B$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$C$2:$C$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$D$2:$D$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$E$2:$E$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$G$2:$G$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4243,7 +5018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4329,6 +5104,7 @@
           <t>component</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>element</t>
@@ -4400,7 +5176,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4415,7 +5191,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4447,12 +5223,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_loss_shredding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bulk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4469,12 +5250,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cfsteel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4489,6 +5275,11 @@
           <t>F_recovered_shredder</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>esteel</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>F_recovered_shredder</t>
@@ -4496,7 +5287,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Mn</t>
         </is>
       </c>
     </row>
@@ -4506,6 +5297,11 @@
           <t>F_refined</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>magnet</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>F_refined</t>
@@ -4513,7 +5309,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Motors</t>
         </is>
       </c>
     </row>
@@ -4530,7 +5326,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Nb</t>
         </is>
       </c>
     </row>
@@ -4547,26 +5343,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Nd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Pr</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Sr</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="E13" t="inlineStr">
+        <is>
+          <t>Tb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
         <is>
           <t>rest</t>
         </is>

--- a/data_folder/bev_electronics/input_data/case.xlsx
+++ b/data_folder/bev_electronics/input_data/case.xlsx
@@ -1570,9 +1570,21 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -1584,7 +1596,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- aluminium oxidises to slag in a pyro route. Carried over unchanged from the Motors_mixed/Al row this replaces, so moving to a real material key changed no value.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1617,9 +1633,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -1631,7 +1659,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- manganese is an alloying element: it follows the steel, not the copper, and oxidises to slag.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1664,9 +1696,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -1678,7 +1722,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- as cfsteel: an alloying element that follows the steel and oxidises to slag.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1711,9 +1759,21 @@
           <t>Sr</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -1725,7 +1785,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- strontium ferrite is a ceramic with no refining route; it reports to slag.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1947,9 +2011,21 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -1961,7 +2037,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1994,9 +2074,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.9625</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
@@ -2008,7 +2100,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2041,9 +2137,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.9625</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2055,7 +2163,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2088,9 +2200,21 @@
           <t>Sr</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -2102,7 +2226,11 @@
           <t>pyro</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2324,9 +2452,21 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -2338,7 +2478,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- aluminium separates reasonably well by eddy current. Carried over from Motors_mixed/Al -- but a bulk aluminium part should separate better than aluminium dispersed through a motor, so this is the first of the four to look up.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2371,9 +2515,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2385,7 +2541,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- manganese rides in the steel, which is magnetically separated at high yield. NOTE WHAT RECOVERED MEANS HERE: present in the recovered steel, not separated as manganese.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2418,9 +2578,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -2432,7 +2604,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- deliberately the same number as cfsteel: nothing I can point to separates the two, so a difference would be invented. Laminated stator steel sits inside a copper winding and may well do worse -- that is the distinction to make first.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2465,9 +2641,21 @@
           <t>Sr</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -2479,7 +2667,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- a shredded ferrite magnet is brittle and pulverises into the fines. Same order as the Nd row.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2701,9 +2893,21 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -2715,7 +2919,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2748,9 +2956,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.325</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -2762,7 +2982,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2795,9 +3019,21 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.325</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -2809,7 +3045,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2842,9 +3082,21 @@
           <t>Sr</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
@@ -2856,7 +3108,11 @@
           <t>hammer_mill</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - the recovery mode, widened by a quarter each way. Replace with a loss measured in its own right.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
